--- a/modules/monitor/assets/modelo-importacao-objetos-semed.xlsx
+++ b/modules/monitor/assets/modelo-importacao-objetos-semed.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OBJETOS" sheetId="1" r:id="R70e48250998f4d40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUÇÕES" sheetId="2" r:id="R96b681dd0a2b4017"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALORES ACEITOS" sheetId="3" r:id="R3524d0b536bd4c31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OBJETOS" sheetId="1" r:id="R14c2dbf6c8534c8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUÇÕES" sheetId="2" r:id="R42b9678da45447e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALORES ACEITOS" sheetId="3" r:id="R7d69c3b0704643d7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,7 +20,7 @@
     <x:numFmt numFmtId="201" formatCode="dd/mm/yyyy"/>
     <x:numFmt numFmtId="202" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="9">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -69,8 +69,24 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF0B2A6F"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF17233C"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF17233C"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -97,8 +113,33 @@
         <x:fgColor rgb="FF176B9B"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F0FF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0B3A5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0B3A5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="12">
+  <x:borders count="17">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -218,11 +259,45 @@
         <x:color rgb="FFC9D6DE"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FF8CAAE6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF8CAAE6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC9D6DE"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFC9D6DE"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC9D6DE"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFD6DEEA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFC9D6DE"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD6DEEA"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="74">
+  <x:cellXfs count="100">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -373,6 +448,60 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -654,10 +783,10 @@
         <x:v>150000</x:v>
       </x:c>
       <x:c r="F2" s="29" t="n">
-        <x:v>46235.625</x:v>
+        <x:v>46235.5</x:v>
       </x:c>
       <x:c r="G2" s="29" t="n">
-        <x:v>46371.625</x:v>
+        <x:v>46371.5</x:v>
       </x:c>
       <x:c r="H2" s="30" t="n">
         <x:f>IF(OR(F2="",G2=""),"",G2-F2)</x:f>
@@ -4264,8 +4393,1802 @@
       <x:c r="M201" s="49"/>
       <x:c r="N201" s="52"/>
     </x:row>
+    <x:row r="202">
+      <x:c r="E202" s="74"/>
+      <x:c r="F202" s="75"/>
+      <x:c r="G202" s="75"/>
+      <x:c r="H202" s="76"/>
+    </x:row>
+    <x:row r="203">
+      <x:c r="E203" s="74"/>
+      <x:c r="F203" s="75"/>
+      <x:c r="G203" s="75"/>
+      <x:c r="H203" s="76"/>
+    </x:row>
+    <x:row r="204">
+      <x:c r="E204" s="74"/>
+      <x:c r="F204" s="75"/>
+      <x:c r="G204" s="75"/>
+      <x:c r="H204" s="76"/>
+    </x:row>
+    <x:row r="205">
+      <x:c r="E205" s="74"/>
+      <x:c r="F205" s="75"/>
+      <x:c r="G205" s="75"/>
+      <x:c r="H205" s="76"/>
+    </x:row>
+    <x:row r="206">
+      <x:c r="E206" s="74"/>
+      <x:c r="F206" s="75"/>
+      <x:c r="G206" s="75"/>
+      <x:c r="H206" s="76"/>
+    </x:row>
+    <x:row r="207">
+      <x:c r="E207" s="74"/>
+      <x:c r="F207" s="75"/>
+      <x:c r="G207" s="75"/>
+      <x:c r="H207" s="76"/>
+    </x:row>
+    <x:row r="208">
+      <x:c r="E208" s="74"/>
+      <x:c r="F208" s="75"/>
+      <x:c r="G208" s="75"/>
+      <x:c r="H208" s="76"/>
+    </x:row>
+    <x:row r="209">
+      <x:c r="E209" s="74"/>
+      <x:c r="F209" s="75"/>
+      <x:c r="G209" s="75"/>
+      <x:c r="H209" s="76"/>
+    </x:row>
+    <x:row r="210">
+      <x:c r="E210" s="74"/>
+      <x:c r="F210" s="75"/>
+      <x:c r="G210" s="75"/>
+      <x:c r="H210" s="76"/>
+    </x:row>
+    <x:row r="211">
+      <x:c r="E211" s="74"/>
+      <x:c r="F211" s="75"/>
+      <x:c r="G211" s="75"/>
+      <x:c r="H211" s="76"/>
+    </x:row>
+    <x:row r="212">
+      <x:c r="E212" s="74"/>
+      <x:c r="F212" s="75"/>
+      <x:c r="G212" s="75"/>
+      <x:c r="H212" s="76"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="E213" s="74"/>
+      <x:c r="F213" s="75"/>
+      <x:c r="G213" s="75"/>
+      <x:c r="H213" s="76"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="E214" s="74"/>
+      <x:c r="F214" s="75"/>
+      <x:c r="G214" s="75"/>
+      <x:c r="H214" s="76"/>
+    </x:row>
+    <x:row r="215">
+      <x:c r="E215" s="74"/>
+      <x:c r="F215" s="75"/>
+      <x:c r="G215" s="75"/>
+      <x:c r="H215" s="76"/>
+    </x:row>
+    <x:row r="216">
+      <x:c r="E216" s="74"/>
+      <x:c r="F216" s="75"/>
+      <x:c r="G216" s="75"/>
+      <x:c r="H216" s="76"/>
+    </x:row>
+    <x:row r="217">
+      <x:c r="E217" s="74"/>
+      <x:c r="F217" s="75"/>
+      <x:c r="G217" s="75"/>
+      <x:c r="H217" s="76"/>
+    </x:row>
+    <x:row r="218">
+      <x:c r="E218" s="74"/>
+      <x:c r="F218" s="75"/>
+      <x:c r="G218" s="75"/>
+      <x:c r="H218" s="76"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="E219" s="74"/>
+      <x:c r="F219" s="75"/>
+      <x:c r="G219" s="75"/>
+      <x:c r="H219" s="76"/>
+    </x:row>
+    <x:row r="220">
+      <x:c r="E220" s="74"/>
+      <x:c r="F220" s="75"/>
+      <x:c r="G220" s="75"/>
+      <x:c r="H220" s="76"/>
+    </x:row>
+    <x:row r="221">
+      <x:c r="E221" s="74"/>
+      <x:c r="F221" s="75"/>
+      <x:c r="G221" s="75"/>
+      <x:c r="H221" s="76"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="E222" s="74"/>
+      <x:c r="F222" s="75"/>
+      <x:c r="G222" s="75"/>
+      <x:c r="H222" s="76"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="E223" s="74"/>
+      <x:c r="F223" s="75"/>
+      <x:c r="G223" s="75"/>
+      <x:c r="H223" s="76"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="E224" s="74"/>
+      <x:c r="F224" s="75"/>
+      <x:c r="G224" s="75"/>
+      <x:c r="H224" s="76"/>
+    </x:row>
+    <x:row r="225">
+      <x:c r="E225" s="74"/>
+      <x:c r="F225" s="75"/>
+      <x:c r="G225" s="75"/>
+      <x:c r="H225" s="76"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="E226" s="74"/>
+      <x:c r="F226" s="75"/>
+      <x:c r="G226" s="75"/>
+      <x:c r="H226" s="76"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="E227" s="74"/>
+      <x:c r="F227" s="75"/>
+      <x:c r="G227" s="75"/>
+      <x:c r="H227" s="76"/>
+    </x:row>
+    <x:row r="228">
+      <x:c r="E228" s="74"/>
+      <x:c r="F228" s="75"/>
+      <x:c r="G228" s="75"/>
+      <x:c r="H228" s="76"/>
+    </x:row>
+    <x:row r="229">
+      <x:c r="E229" s="74"/>
+      <x:c r="F229" s="75"/>
+      <x:c r="G229" s="75"/>
+      <x:c r="H229" s="76"/>
+    </x:row>
+    <x:row r="230">
+      <x:c r="E230" s="74"/>
+      <x:c r="F230" s="75"/>
+      <x:c r="G230" s="75"/>
+      <x:c r="H230" s="76"/>
+    </x:row>
+    <x:row r="231">
+      <x:c r="E231" s="74"/>
+      <x:c r="F231" s="75"/>
+      <x:c r="G231" s="75"/>
+      <x:c r="H231" s="76"/>
+    </x:row>
+    <x:row r="232">
+      <x:c r="E232" s="74"/>
+      <x:c r="F232" s="75"/>
+      <x:c r="G232" s="75"/>
+      <x:c r="H232" s="76"/>
+    </x:row>
+    <x:row r="233">
+      <x:c r="E233" s="74"/>
+      <x:c r="F233" s="75"/>
+      <x:c r="G233" s="75"/>
+      <x:c r="H233" s="76"/>
+    </x:row>
+    <x:row r="234">
+      <x:c r="E234" s="74"/>
+      <x:c r="F234" s="75"/>
+      <x:c r="G234" s="75"/>
+      <x:c r="H234" s="76"/>
+    </x:row>
+    <x:row r="235">
+      <x:c r="E235" s="74"/>
+      <x:c r="F235" s="75"/>
+      <x:c r="G235" s="75"/>
+      <x:c r="H235" s="76"/>
+    </x:row>
+    <x:row r="236">
+      <x:c r="E236" s="74"/>
+      <x:c r="F236" s="75"/>
+      <x:c r="G236" s="75"/>
+      <x:c r="H236" s="76"/>
+    </x:row>
+    <x:row r="237">
+      <x:c r="E237" s="74"/>
+      <x:c r="F237" s="75"/>
+      <x:c r="G237" s="75"/>
+      <x:c r="H237" s="76"/>
+    </x:row>
+    <x:row r="238">
+      <x:c r="E238" s="74"/>
+      <x:c r="F238" s="75"/>
+      <x:c r="G238" s="75"/>
+      <x:c r="H238" s="76"/>
+    </x:row>
+    <x:row r="239">
+      <x:c r="E239" s="74"/>
+      <x:c r="F239" s="75"/>
+      <x:c r="G239" s="75"/>
+      <x:c r="H239" s="76"/>
+    </x:row>
+    <x:row r="240">
+      <x:c r="E240" s="74"/>
+      <x:c r="F240" s="75"/>
+      <x:c r="G240" s="75"/>
+      <x:c r="H240" s="76"/>
+    </x:row>
+    <x:row r="241">
+      <x:c r="E241" s="74"/>
+      <x:c r="F241" s="75"/>
+      <x:c r="G241" s="75"/>
+      <x:c r="H241" s="76"/>
+    </x:row>
+    <x:row r="242">
+      <x:c r="E242" s="74"/>
+      <x:c r="F242" s="75"/>
+      <x:c r="G242" s="75"/>
+      <x:c r="H242" s="76"/>
+    </x:row>
+    <x:row r="243">
+      <x:c r="E243" s="74"/>
+      <x:c r="F243" s="75"/>
+      <x:c r="G243" s="75"/>
+      <x:c r="H243" s="76"/>
+    </x:row>
+    <x:row r="244">
+      <x:c r="E244" s="74"/>
+      <x:c r="F244" s="75"/>
+      <x:c r="G244" s="75"/>
+      <x:c r="H244" s="76"/>
+    </x:row>
+    <x:row r="245">
+      <x:c r="E245" s="74"/>
+      <x:c r="F245" s="75"/>
+      <x:c r="G245" s="75"/>
+      <x:c r="H245" s="76"/>
+    </x:row>
+    <x:row r="246">
+      <x:c r="E246" s="74"/>
+      <x:c r="F246" s="75"/>
+      <x:c r="G246" s="75"/>
+      <x:c r="H246" s="76"/>
+    </x:row>
+    <x:row r="247">
+      <x:c r="E247" s="74"/>
+      <x:c r="F247" s="75"/>
+      <x:c r="G247" s="75"/>
+      <x:c r="H247" s="76"/>
+    </x:row>
+    <x:row r="248">
+      <x:c r="E248" s="74"/>
+      <x:c r="F248" s="75"/>
+      <x:c r="G248" s="75"/>
+      <x:c r="H248" s="76"/>
+    </x:row>
+    <x:row r="249">
+      <x:c r="E249" s="74"/>
+      <x:c r="F249" s="75"/>
+      <x:c r="G249" s="75"/>
+      <x:c r="H249" s="76"/>
+    </x:row>
+    <x:row r="250">
+      <x:c r="E250" s="74"/>
+      <x:c r="F250" s="75"/>
+      <x:c r="G250" s="75"/>
+      <x:c r="H250" s="76"/>
+    </x:row>
+    <x:row r="251">
+      <x:c r="E251" s="74"/>
+      <x:c r="F251" s="75"/>
+      <x:c r="G251" s="75"/>
+      <x:c r="H251" s="76"/>
+    </x:row>
+    <x:row r="252">
+      <x:c r="E252" s="74"/>
+      <x:c r="F252" s="75"/>
+      <x:c r="G252" s="75"/>
+      <x:c r="H252" s="76"/>
+    </x:row>
+    <x:row r="253">
+      <x:c r="E253" s="74"/>
+      <x:c r="F253" s="75"/>
+      <x:c r="G253" s="75"/>
+      <x:c r="H253" s="76"/>
+    </x:row>
+    <x:row r="254">
+      <x:c r="E254" s="74"/>
+      <x:c r="F254" s="75"/>
+      <x:c r="G254" s="75"/>
+      <x:c r="H254" s="76"/>
+    </x:row>
+    <x:row r="255">
+      <x:c r="E255" s="74"/>
+      <x:c r="F255" s="75"/>
+      <x:c r="G255" s="75"/>
+      <x:c r="H255" s="76"/>
+    </x:row>
+    <x:row r="256">
+      <x:c r="E256" s="74"/>
+      <x:c r="F256" s="75"/>
+      <x:c r="G256" s="75"/>
+      <x:c r="H256" s="76"/>
+    </x:row>
+    <x:row r="257">
+      <x:c r="E257" s="74"/>
+      <x:c r="F257" s="75"/>
+      <x:c r="G257" s="75"/>
+      <x:c r="H257" s="76"/>
+    </x:row>
+    <x:row r="258">
+      <x:c r="E258" s="74"/>
+      <x:c r="F258" s="75"/>
+      <x:c r="G258" s="75"/>
+      <x:c r="H258" s="76"/>
+    </x:row>
+    <x:row r="259">
+      <x:c r="E259" s="74"/>
+      <x:c r="F259" s="75"/>
+      <x:c r="G259" s="75"/>
+      <x:c r="H259" s="76"/>
+    </x:row>
+    <x:row r="260">
+      <x:c r="E260" s="74"/>
+      <x:c r="F260" s="75"/>
+      <x:c r="G260" s="75"/>
+      <x:c r="H260" s="76"/>
+    </x:row>
+    <x:row r="261">
+      <x:c r="E261" s="74"/>
+      <x:c r="F261" s="75"/>
+      <x:c r="G261" s="75"/>
+      <x:c r="H261" s="76"/>
+    </x:row>
+    <x:row r="262">
+      <x:c r="E262" s="74"/>
+      <x:c r="F262" s="75"/>
+      <x:c r="G262" s="75"/>
+      <x:c r="H262" s="76"/>
+    </x:row>
+    <x:row r="263">
+      <x:c r="E263" s="74"/>
+      <x:c r="F263" s="75"/>
+      <x:c r="G263" s="75"/>
+      <x:c r="H263" s="76"/>
+    </x:row>
+    <x:row r="264">
+      <x:c r="E264" s="74"/>
+      <x:c r="F264" s="75"/>
+      <x:c r="G264" s="75"/>
+      <x:c r="H264" s="76"/>
+    </x:row>
+    <x:row r="265">
+      <x:c r="E265" s="74"/>
+      <x:c r="F265" s="75"/>
+      <x:c r="G265" s="75"/>
+      <x:c r="H265" s="76"/>
+    </x:row>
+    <x:row r="266">
+      <x:c r="E266" s="74"/>
+      <x:c r="F266" s="75"/>
+      <x:c r="G266" s="75"/>
+      <x:c r="H266" s="76"/>
+    </x:row>
+    <x:row r="267">
+      <x:c r="E267" s="74"/>
+      <x:c r="F267" s="75"/>
+      <x:c r="G267" s="75"/>
+      <x:c r="H267" s="76"/>
+    </x:row>
+    <x:row r="268">
+      <x:c r="E268" s="74"/>
+      <x:c r="F268" s="75"/>
+      <x:c r="G268" s="75"/>
+      <x:c r="H268" s="76"/>
+    </x:row>
+    <x:row r="269">
+      <x:c r="E269" s="74"/>
+      <x:c r="F269" s="75"/>
+      <x:c r="G269" s="75"/>
+      <x:c r="H269" s="76"/>
+    </x:row>
+    <x:row r="270">
+      <x:c r="E270" s="74"/>
+      <x:c r="F270" s="75"/>
+      <x:c r="G270" s="75"/>
+      <x:c r="H270" s="76"/>
+    </x:row>
+    <x:row r="271">
+      <x:c r="E271" s="74"/>
+      <x:c r="F271" s="75"/>
+      <x:c r="G271" s="75"/>
+      <x:c r="H271" s="76"/>
+    </x:row>
+    <x:row r="272">
+      <x:c r="E272" s="74"/>
+      <x:c r="F272" s="75"/>
+      <x:c r="G272" s="75"/>
+      <x:c r="H272" s="76"/>
+    </x:row>
+    <x:row r="273">
+      <x:c r="E273" s="74"/>
+      <x:c r="F273" s="75"/>
+      <x:c r="G273" s="75"/>
+      <x:c r="H273" s="76"/>
+    </x:row>
+    <x:row r="274">
+      <x:c r="E274" s="74"/>
+      <x:c r="F274" s="75"/>
+      <x:c r="G274" s="75"/>
+      <x:c r="H274" s="76"/>
+    </x:row>
+    <x:row r="275">
+      <x:c r="E275" s="74"/>
+      <x:c r="F275" s="75"/>
+      <x:c r="G275" s="75"/>
+      <x:c r="H275" s="76"/>
+    </x:row>
+    <x:row r="276">
+      <x:c r="E276" s="74"/>
+      <x:c r="F276" s="75"/>
+      <x:c r="G276" s="75"/>
+      <x:c r="H276" s="76"/>
+    </x:row>
+    <x:row r="277">
+      <x:c r="E277" s="74"/>
+      <x:c r="F277" s="75"/>
+      <x:c r="G277" s="75"/>
+      <x:c r="H277" s="76"/>
+    </x:row>
+    <x:row r="278">
+      <x:c r="E278" s="74"/>
+      <x:c r="F278" s="75"/>
+      <x:c r="G278" s="75"/>
+      <x:c r="H278" s="76"/>
+    </x:row>
+    <x:row r="279">
+      <x:c r="E279" s="74"/>
+      <x:c r="F279" s="75"/>
+      <x:c r="G279" s="75"/>
+      <x:c r="H279" s="76"/>
+    </x:row>
+    <x:row r="280">
+      <x:c r="E280" s="74"/>
+      <x:c r="F280" s="75"/>
+      <x:c r="G280" s="75"/>
+      <x:c r="H280" s="76"/>
+    </x:row>
+    <x:row r="281">
+      <x:c r="E281" s="74"/>
+      <x:c r="F281" s="75"/>
+      <x:c r="G281" s="75"/>
+      <x:c r="H281" s="76"/>
+    </x:row>
+    <x:row r="282">
+      <x:c r="E282" s="74"/>
+      <x:c r="F282" s="75"/>
+      <x:c r="G282" s="75"/>
+      <x:c r="H282" s="76"/>
+    </x:row>
+    <x:row r="283">
+      <x:c r="E283" s="74"/>
+      <x:c r="F283" s="75"/>
+      <x:c r="G283" s="75"/>
+      <x:c r="H283" s="76"/>
+    </x:row>
+    <x:row r="284">
+      <x:c r="E284" s="74"/>
+      <x:c r="F284" s="75"/>
+      <x:c r="G284" s="75"/>
+      <x:c r="H284" s="76"/>
+    </x:row>
+    <x:row r="285">
+      <x:c r="E285" s="74"/>
+      <x:c r="F285" s="75"/>
+      <x:c r="G285" s="75"/>
+      <x:c r="H285" s="76"/>
+    </x:row>
+    <x:row r="286">
+      <x:c r="E286" s="74"/>
+      <x:c r="F286" s="75"/>
+      <x:c r="G286" s="75"/>
+      <x:c r="H286" s="76"/>
+    </x:row>
+    <x:row r="287">
+      <x:c r="E287" s="74"/>
+      <x:c r="F287" s="75"/>
+      <x:c r="G287" s="75"/>
+      <x:c r="H287" s="76"/>
+    </x:row>
+    <x:row r="288">
+      <x:c r="E288" s="74"/>
+      <x:c r="F288" s="75"/>
+      <x:c r="G288" s="75"/>
+      <x:c r="H288" s="76"/>
+    </x:row>
+    <x:row r="289">
+      <x:c r="E289" s="74"/>
+      <x:c r="F289" s="75"/>
+      <x:c r="G289" s="75"/>
+      <x:c r="H289" s="76"/>
+    </x:row>
+    <x:row r="290">
+      <x:c r="E290" s="74"/>
+      <x:c r="F290" s="75"/>
+      <x:c r="G290" s="75"/>
+      <x:c r="H290" s="76"/>
+    </x:row>
+    <x:row r="291">
+      <x:c r="E291" s="74"/>
+      <x:c r="F291" s="75"/>
+      <x:c r="G291" s="75"/>
+      <x:c r="H291" s="76"/>
+    </x:row>
+    <x:row r="292">
+      <x:c r="E292" s="74"/>
+      <x:c r="F292" s="75"/>
+      <x:c r="G292" s="75"/>
+      <x:c r="H292" s="76"/>
+    </x:row>
+    <x:row r="293">
+      <x:c r="E293" s="74"/>
+      <x:c r="F293" s="75"/>
+      <x:c r="G293" s="75"/>
+      <x:c r="H293" s="76"/>
+    </x:row>
+    <x:row r="294">
+      <x:c r="E294" s="74"/>
+      <x:c r="F294" s="75"/>
+      <x:c r="G294" s="75"/>
+      <x:c r="H294" s="76"/>
+    </x:row>
+    <x:row r="295">
+      <x:c r="E295" s="74"/>
+      <x:c r="F295" s="75"/>
+      <x:c r="G295" s="75"/>
+      <x:c r="H295" s="76"/>
+    </x:row>
+    <x:row r="296">
+      <x:c r="E296" s="74"/>
+      <x:c r="F296" s="75"/>
+      <x:c r="G296" s="75"/>
+      <x:c r="H296" s="76"/>
+    </x:row>
+    <x:row r="297">
+      <x:c r="E297" s="74"/>
+      <x:c r="F297" s="75"/>
+      <x:c r="G297" s="75"/>
+      <x:c r="H297" s="76"/>
+    </x:row>
+    <x:row r="298">
+      <x:c r="E298" s="74"/>
+      <x:c r="F298" s="75"/>
+      <x:c r="G298" s="75"/>
+      <x:c r="H298" s="76"/>
+    </x:row>
+    <x:row r="299">
+      <x:c r="E299" s="74"/>
+      <x:c r="F299" s="75"/>
+      <x:c r="G299" s="75"/>
+      <x:c r="H299" s="76"/>
+    </x:row>
+    <x:row r="300">
+      <x:c r="E300" s="74"/>
+      <x:c r="F300" s="75"/>
+      <x:c r="G300" s="75"/>
+      <x:c r="H300" s="76"/>
+    </x:row>
+    <x:row r="301">
+      <x:c r="E301" s="74"/>
+      <x:c r="F301" s="75"/>
+      <x:c r="G301" s="75"/>
+      <x:c r="H301" s="76"/>
+    </x:row>
+    <x:row r="302">
+      <x:c r="E302" s="74"/>
+      <x:c r="F302" s="75"/>
+      <x:c r="G302" s="75"/>
+      <x:c r="H302" s="76"/>
+    </x:row>
+    <x:row r="303">
+      <x:c r="E303" s="74"/>
+      <x:c r="F303" s="75"/>
+      <x:c r="G303" s="75"/>
+      <x:c r="H303" s="76"/>
+    </x:row>
+    <x:row r="304">
+      <x:c r="E304" s="74"/>
+      <x:c r="F304" s="75"/>
+      <x:c r="G304" s="75"/>
+      <x:c r="H304" s="76"/>
+    </x:row>
+    <x:row r="305">
+      <x:c r="E305" s="74"/>
+      <x:c r="F305" s="75"/>
+      <x:c r="G305" s="75"/>
+      <x:c r="H305" s="76"/>
+    </x:row>
+    <x:row r="306">
+      <x:c r="E306" s="74"/>
+      <x:c r="F306" s="75"/>
+      <x:c r="G306" s="75"/>
+      <x:c r="H306" s="76"/>
+    </x:row>
+    <x:row r="307">
+      <x:c r="E307" s="74"/>
+      <x:c r="F307" s="75"/>
+      <x:c r="G307" s="75"/>
+      <x:c r="H307" s="76"/>
+    </x:row>
+    <x:row r="308">
+      <x:c r="E308" s="74"/>
+      <x:c r="F308" s="75"/>
+      <x:c r="G308" s="75"/>
+      <x:c r="H308" s="76"/>
+    </x:row>
+    <x:row r="309">
+      <x:c r="E309" s="74"/>
+      <x:c r="F309" s="75"/>
+      <x:c r="G309" s="75"/>
+      <x:c r="H309" s="76"/>
+    </x:row>
+    <x:row r="310">
+      <x:c r="E310" s="74"/>
+      <x:c r="F310" s="75"/>
+      <x:c r="G310" s="75"/>
+      <x:c r="H310" s="76"/>
+    </x:row>
+    <x:row r="311">
+      <x:c r="E311" s="74"/>
+      <x:c r="F311" s="75"/>
+      <x:c r="G311" s="75"/>
+      <x:c r="H311" s="76"/>
+    </x:row>
+    <x:row r="312">
+      <x:c r="E312" s="74"/>
+      <x:c r="F312" s="75"/>
+      <x:c r="G312" s="75"/>
+      <x:c r="H312" s="76"/>
+    </x:row>
+    <x:row r="313">
+      <x:c r="E313" s="74"/>
+      <x:c r="F313" s="75"/>
+      <x:c r="G313" s="75"/>
+      <x:c r="H313" s="76"/>
+    </x:row>
+    <x:row r="314">
+      <x:c r="E314" s="74"/>
+      <x:c r="F314" s="75"/>
+      <x:c r="G314" s="75"/>
+      <x:c r="H314" s="76"/>
+    </x:row>
+    <x:row r="315">
+      <x:c r="E315" s="74"/>
+      <x:c r="F315" s="75"/>
+      <x:c r="G315" s="75"/>
+      <x:c r="H315" s="76"/>
+    </x:row>
+    <x:row r="316">
+      <x:c r="E316" s="74"/>
+      <x:c r="F316" s="75"/>
+      <x:c r="G316" s="75"/>
+      <x:c r="H316" s="76"/>
+    </x:row>
+    <x:row r="317">
+      <x:c r="E317" s="74"/>
+      <x:c r="F317" s="75"/>
+      <x:c r="G317" s="75"/>
+      <x:c r="H317" s="76"/>
+    </x:row>
+    <x:row r="318">
+      <x:c r="E318" s="74"/>
+      <x:c r="F318" s="75"/>
+      <x:c r="G318" s="75"/>
+      <x:c r="H318" s="76"/>
+    </x:row>
+    <x:row r="319">
+      <x:c r="E319" s="74"/>
+      <x:c r="F319" s="75"/>
+      <x:c r="G319" s="75"/>
+      <x:c r="H319" s="76"/>
+    </x:row>
+    <x:row r="320">
+      <x:c r="E320" s="74"/>
+      <x:c r="F320" s="75"/>
+      <x:c r="G320" s="75"/>
+      <x:c r="H320" s="76"/>
+    </x:row>
+    <x:row r="321">
+      <x:c r="E321" s="74"/>
+      <x:c r="F321" s="75"/>
+      <x:c r="G321" s="75"/>
+      <x:c r="H321" s="76"/>
+    </x:row>
+    <x:row r="322">
+      <x:c r="E322" s="74"/>
+      <x:c r="F322" s="75"/>
+      <x:c r="G322" s="75"/>
+      <x:c r="H322" s="76"/>
+    </x:row>
+    <x:row r="323">
+      <x:c r="E323" s="74"/>
+      <x:c r="F323" s="75"/>
+      <x:c r="G323" s="75"/>
+      <x:c r="H323" s="76"/>
+    </x:row>
+    <x:row r="324">
+      <x:c r="E324" s="74"/>
+      <x:c r="F324" s="75"/>
+      <x:c r="G324" s="75"/>
+      <x:c r="H324" s="76"/>
+    </x:row>
+    <x:row r="325">
+      <x:c r="E325" s="74"/>
+      <x:c r="F325" s="75"/>
+      <x:c r="G325" s="75"/>
+      <x:c r="H325" s="76"/>
+    </x:row>
+    <x:row r="326">
+      <x:c r="E326" s="74"/>
+      <x:c r="F326" s="75"/>
+      <x:c r="G326" s="75"/>
+      <x:c r="H326" s="76"/>
+    </x:row>
+    <x:row r="327">
+      <x:c r="E327" s="74"/>
+      <x:c r="F327" s="75"/>
+      <x:c r="G327" s="75"/>
+      <x:c r="H327" s="76"/>
+    </x:row>
+    <x:row r="328">
+      <x:c r="E328" s="74"/>
+      <x:c r="F328" s="75"/>
+      <x:c r="G328" s="75"/>
+      <x:c r="H328" s="76"/>
+    </x:row>
+    <x:row r="329">
+      <x:c r="E329" s="74"/>
+      <x:c r="F329" s="75"/>
+      <x:c r="G329" s="75"/>
+      <x:c r="H329" s="76"/>
+    </x:row>
+    <x:row r="330">
+      <x:c r="E330" s="74"/>
+      <x:c r="F330" s="75"/>
+      <x:c r="G330" s="75"/>
+      <x:c r="H330" s="76"/>
+    </x:row>
+    <x:row r="331">
+      <x:c r="E331" s="74"/>
+      <x:c r="F331" s="75"/>
+      <x:c r="G331" s="75"/>
+      <x:c r="H331" s="76"/>
+    </x:row>
+    <x:row r="332">
+      <x:c r="E332" s="74"/>
+      <x:c r="F332" s="75"/>
+      <x:c r="G332" s="75"/>
+      <x:c r="H332" s="76"/>
+    </x:row>
+    <x:row r="333">
+      <x:c r="E333" s="74"/>
+      <x:c r="F333" s="75"/>
+      <x:c r="G333" s="75"/>
+      <x:c r="H333" s="76"/>
+    </x:row>
+    <x:row r="334">
+      <x:c r="E334" s="74"/>
+      <x:c r="F334" s="75"/>
+      <x:c r="G334" s="75"/>
+      <x:c r="H334" s="76"/>
+    </x:row>
+    <x:row r="335">
+      <x:c r="E335" s="74"/>
+      <x:c r="F335" s="75"/>
+      <x:c r="G335" s="75"/>
+      <x:c r="H335" s="76"/>
+    </x:row>
+    <x:row r="336">
+      <x:c r="E336" s="74"/>
+      <x:c r="F336" s="75"/>
+      <x:c r="G336" s="75"/>
+      <x:c r="H336" s="76"/>
+    </x:row>
+    <x:row r="337">
+      <x:c r="E337" s="74"/>
+      <x:c r="F337" s="75"/>
+      <x:c r="G337" s="75"/>
+      <x:c r="H337" s="76"/>
+    </x:row>
+    <x:row r="338">
+      <x:c r="E338" s="74"/>
+      <x:c r="F338" s="75"/>
+      <x:c r="G338" s="75"/>
+      <x:c r="H338" s="76"/>
+    </x:row>
+    <x:row r="339">
+      <x:c r="E339" s="74"/>
+      <x:c r="F339" s="75"/>
+      <x:c r="G339" s="75"/>
+      <x:c r="H339" s="76"/>
+    </x:row>
+    <x:row r="340">
+      <x:c r="E340" s="74"/>
+      <x:c r="F340" s="75"/>
+      <x:c r="G340" s="75"/>
+      <x:c r="H340" s="76"/>
+    </x:row>
+    <x:row r="341">
+      <x:c r="E341" s="74"/>
+      <x:c r="F341" s="75"/>
+      <x:c r="G341" s="75"/>
+      <x:c r="H341" s="76"/>
+    </x:row>
+    <x:row r="342">
+      <x:c r="E342" s="74"/>
+      <x:c r="F342" s="75"/>
+      <x:c r="G342" s="75"/>
+      <x:c r="H342" s="76"/>
+    </x:row>
+    <x:row r="343">
+      <x:c r="E343" s="74"/>
+      <x:c r="F343" s="75"/>
+      <x:c r="G343" s="75"/>
+      <x:c r="H343" s="76"/>
+    </x:row>
+    <x:row r="344">
+      <x:c r="E344" s="74"/>
+      <x:c r="F344" s="75"/>
+      <x:c r="G344" s="75"/>
+      <x:c r="H344" s="76"/>
+    </x:row>
+    <x:row r="345">
+      <x:c r="E345" s="74"/>
+      <x:c r="F345" s="75"/>
+      <x:c r="G345" s="75"/>
+      <x:c r="H345" s="76"/>
+    </x:row>
+    <x:row r="346">
+      <x:c r="E346" s="74"/>
+      <x:c r="F346" s="75"/>
+      <x:c r="G346" s="75"/>
+      <x:c r="H346" s="76"/>
+    </x:row>
+    <x:row r="347">
+      <x:c r="E347" s="74"/>
+      <x:c r="F347" s="75"/>
+      <x:c r="G347" s="75"/>
+      <x:c r="H347" s="76"/>
+    </x:row>
+    <x:row r="348">
+      <x:c r="E348" s="74"/>
+      <x:c r="F348" s="75"/>
+      <x:c r="G348" s="75"/>
+      <x:c r="H348" s="76"/>
+    </x:row>
+    <x:row r="349">
+      <x:c r="E349" s="74"/>
+      <x:c r="F349" s="75"/>
+      <x:c r="G349" s="75"/>
+      <x:c r="H349" s="76"/>
+    </x:row>
+    <x:row r="350">
+      <x:c r="E350" s="74"/>
+      <x:c r="F350" s="75"/>
+      <x:c r="G350" s="75"/>
+      <x:c r="H350" s="76"/>
+    </x:row>
+    <x:row r="351">
+      <x:c r="E351" s="74"/>
+      <x:c r="F351" s="75"/>
+      <x:c r="G351" s="75"/>
+      <x:c r="H351" s="76"/>
+    </x:row>
+    <x:row r="352">
+      <x:c r="E352" s="74"/>
+      <x:c r="F352" s="75"/>
+      <x:c r="G352" s="75"/>
+      <x:c r="H352" s="76"/>
+    </x:row>
+    <x:row r="353">
+      <x:c r="E353" s="74"/>
+      <x:c r="F353" s="75"/>
+      <x:c r="G353" s="75"/>
+      <x:c r="H353" s="76"/>
+    </x:row>
+    <x:row r="354">
+      <x:c r="E354" s="74"/>
+      <x:c r="F354" s="75"/>
+      <x:c r="G354" s="75"/>
+      <x:c r="H354" s="76"/>
+    </x:row>
+    <x:row r="355">
+      <x:c r="E355" s="74"/>
+      <x:c r="F355" s="75"/>
+      <x:c r="G355" s="75"/>
+      <x:c r="H355" s="76"/>
+    </x:row>
+    <x:row r="356">
+      <x:c r="E356" s="74"/>
+      <x:c r="F356" s="75"/>
+      <x:c r="G356" s="75"/>
+      <x:c r="H356" s="76"/>
+    </x:row>
+    <x:row r="357">
+      <x:c r="E357" s="74"/>
+      <x:c r="F357" s="75"/>
+      <x:c r="G357" s="75"/>
+      <x:c r="H357" s="76"/>
+    </x:row>
+    <x:row r="358">
+      <x:c r="E358" s="74"/>
+      <x:c r="F358" s="75"/>
+      <x:c r="G358" s="75"/>
+      <x:c r="H358" s="76"/>
+    </x:row>
+    <x:row r="359">
+      <x:c r="E359" s="74"/>
+      <x:c r="F359" s="75"/>
+      <x:c r="G359" s="75"/>
+      <x:c r="H359" s="76"/>
+    </x:row>
+    <x:row r="360">
+      <x:c r="E360" s="74"/>
+      <x:c r="F360" s="75"/>
+      <x:c r="G360" s="75"/>
+      <x:c r="H360" s="76"/>
+    </x:row>
+    <x:row r="361">
+      <x:c r="E361" s="74"/>
+      <x:c r="F361" s="75"/>
+      <x:c r="G361" s="75"/>
+      <x:c r="H361" s="76"/>
+    </x:row>
+    <x:row r="362">
+      <x:c r="E362" s="74"/>
+      <x:c r="F362" s="75"/>
+      <x:c r="G362" s="75"/>
+      <x:c r="H362" s="76"/>
+    </x:row>
+    <x:row r="363">
+      <x:c r="E363" s="74"/>
+      <x:c r="F363" s="75"/>
+      <x:c r="G363" s="75"/>
+      <x:c r="H363" s="76"/>
+    </x:row>
+    <x:row r="364">
+      <x:c r="E364" s="74"/>
+      <x:c r="F364" s="75"/>
+      <x:c r="G364" s="75"/>
+      <x:c r="H364" s="76"/>
+    </x:row>
+    <x:row r="365">
+      <x:c r="E365" s="74"/>
+      <x:c r="F365" s="75"/>
+      <x:c r="G365" s="75"/>
+      <x:c r="H365" s="76"/>
+    </x:row>
+    <x:row r="366">
+      <x:c r="E366" s="74"/>
+      <x:c r="F366" s="75"/>
+      <x:c r="G366" s="75"/>
+      <x:c r="H366" s="76"/>
+    </x:row>
+    <x:row r="367">
+      <x:c r="E367" s="74"/>
+      <x:c r="F367" s="75"/>
+      <x:c r="G367" s="75"/>
+      <x:c r="H367" s="76"/>
+    </x:row>
+    <x:row r="368">
+      <x:c r="E368" s="74"/>
+      <x:c r="F368" s="75"/>
+      <x:c r="G368" s="75"/>
+      <x:c r="H368" s="76"/>
+    </x:row>
+    <x:row r="369">
+      <x:c r="E369" s="74"/>
+      <x:c r="F369" s="75"/>
+      <x:c r="G369" s="75"/>
+      <x:c r="H369" s="76"/>
+    </x:row>
+    <x:row r="370">
+      <x:c r="E370" s="74"/>
+      <x:c r="F370" s="75"/>
+      <x:c r="G370" s="75"/>
+      <x:c r="H370" s="76"/>
+    </x:row>
+    <x:row r="371">
+      <x:c r="E371" s="74"/>
+      <x:c r="F371" s="75"/>
+      <x:c r="G371" s="75"/>
+      <x:c r="H371" s="76"/>
+    </x:row>
+    <x:row r="372">
+      <x:c r="E372" s="74"/>
+      <x:c r="F372" s="75"/>
+      <x:c r="G372" s="75"/>
+      <x:c r="H372" s="76"/>
+    </x:row>
+    <x:row r="373">
+      <x:c r="E373" s="74"/>
+      <x:c r="F373" s="75"/>
+      <x:c r="G373" s="75"/>
+      <x:c r="H373" s="76"/>
+    </x:row>
+    <x:row r="374">
+      <x:c r="E374" s="74"/>
+      <x:c r="F374" s="75"/>
+      <x:c r="G374" s="75"/>
+      <x:c r="H374" s="76"/>
+    </x:row>
+    <x:row r="375">
+      <x:c r="E375" s="74"/>
+      <x:c r="F375" s="75"/>
+      <x:c r="G375" s="75"/>
+      <x:c r="H375" s="76"/>
+    </x:row>
+    <x:row r="376">
+      <x:c r="E376" s="74"/>
+      <x:c r="F376" s="75"/>
+      <x:c r="G376" s="75"/>
+      <x:c r="H376" s="76"/>
+    </x:row>
+    <x:row r="377">
+      <x:c r="E377" s="74"/>
+      <x:c r="F377" s="75"/>
+      <x:c r="G377" s="75"/>
+      <x:c r="H377" s="76"/>
+    </x:row>
+    <x:row r="378">
+      <x:c r="E378" s="74"/>
+      <x:c r="F378" s="75"/>
+      <x:c r="G378" s="75"/>
+      <x:c r="H378" s="76"/>
+    </x:row>
+    <x:row r="379">
+      <x:c r="E379" s="74"/>
+      <x:c r="F379" s="75"/>
+      <x:c r="G379" s="75"/>
+      <x:c r="H379" s="76"/>
+    </x:row>
+    <x:row r="380">
+      <x:c r="E380" s="74"/>
+      <x:c r="F380" s="75"/>
+      <x:c r="G380" s="75"/>
+      <x:c r="H380" s="76"/>
+    </x:row>
+    <x:row r="381">
+      <x:c r="E381" s="74"/>
+      <x:c r="F381" s="75"/>
+      <x:c r="G381" s="75"/>
+      <x:c r="H381" s="76"/>
+    </x:row>
+    <x:row r="382">
+      <x:c r="E382" s="74"/>
+      <x:c r="F382" s="75"/>
+      <x:c r="G382" s="75"/>
+      <x:c r="H382" s="76"/>
+    </x:row>
+    <x:row r="383">
+      <x:c r="E383" s="74"/>
+      <x:c r="F383" s="75"/>
+      <x:c r="G383" s="75"/>
+      <x:c r="H383" s="76"/>
+    </x:row>
+    <x:row r="384">
+      <x:c r="E384" s="74"/>
+      <x:c r="F384" s="75"/>
+      <x:c r="G384" s="75"/>
+      <x:c r="H384" s="76"/>
+    </x:row>
+    <x:row r="385">
+      <x:c r="E385" s="74"/>
+      <x:c r="F385" s="75"/>
+      <x:c r="G385" s="75"/>
+      <x:c r="H385" s="76"/>
+    </x:row>
+    <x:row r="386">
+      <x:c r="E386" s="74"/>
+      <x:c r="F386" s="75"/>
+      <x:c r="G386" s="75"/>
+      <x:c r="H386" s="76"/>
+    </x:row>
+    <x:row r="387">
+      <x:c r="E387" s="74"/>
+      <x:c r="F387" s="75"/>
+      <x:c r="G387" s="75"/>
+      <x:c r="H387" s="76"/>
+    </x:row>
+    <x:row r="388">
+      <x:c r="E388" s="74"/>
+      <x:c r="F388" s="75"/>
+      <x:c r="G388" s="75"/>
+      <x:c r="H388" s="76"/>
+    </x:row>
+    <x:row r="389">
+      <x:c r="E389" s="74"/>
+      <x:c r="F389" s="75"/>
+      <x:c r="G389" s="75"/>
+      <x:c r="H389" s="76"/>
+    </x:row>
+    <x:row r="390">
+      <x:c r="E390" s="74"/>
+      <x:c r="F390" s="75"/>
+      <x:c r="G390" s="75"/>
+      <x:c r="H390" s="76"/>
+    </x:row>
+    <x:row r="391">
+      <x:c r="E391" s="74"/>
+      <x:c r="F391" s="75"/>
+      <x:c r="G391" s="75"/>
+      <x:c r="H391" s="76"/>
+    </x:row>
+    <x:row r="392">
+      <x:c r="E392" s="74"/>
+      <x:c r="F392" s="75"/>
+      <x:c r="G392" s="75"/>
+      <x:c r="H392" s="76"/>
+    </x:row>
+    <x:row r="393">
+      <x:c r="E393" s="74"/>
+      <x:c r="F393" s="75"/>
+      <x:c r="G393" s="75"/>
+      <x:c r="H393" s="76"/>
+    </x:row>
+    <x:row r="394">
+      <x:c r="E394" s="74"/>
+      <x:c r="F394" s="75"/>
+      <x:c r="G394" s="75"/>
+      <x:c r="H394" s="76"/>
+    </x:row>
+    <x:row r="395">
+      <x:c r="E395" s="74"/>
+      <x:c r="F395" s="75"/>
+      <x:c r="G395" s="75"/>
+      <x:c r="H395" s="76"/>
+    </x:row>
+    <x:row r="396">
+      <x:c r="E396" s="74"/>
+      <x:c r="F396" s="75"/>
+      <x:c r="G396" s="75"/>
+      <x:c r="H396" s="76"/>
+    </x:row>
+    <x:row r="397">
+      <x:c r="E397" s="74"/>
+      <x:c r="F397" s="75"/>
+      <x:c r="G397" s="75"/>
+      <x:c r="H397" s="76"/>
+    </x:row>
+    <x:row r="398">
+      <x:c r="E398" s="74"/>
+      <x:c r="F398" s="75"/>
+      <x:c r="G398" s="75"/>
+      <x:c r="H398" s="76"/>
+    </x:row>
+    <x:row r="399">
+      <x:c r="E399" s="74"/>
+      <x:c r="F399" s="75"/>
+      <x:c r="G399" s="75"/>
+      <x:c r="H399" s="76"/>
+    </x:row>
+    <x:row r="400">
+      <x:c r="E400" s="74"/>
+      <x:c r="F400" s="75"/>
+      <x:c r="G400" s="75"/>
+      <x:c r="H400" s="76"/>
+    </x:row>
+    <x:row r="401">
+      <x:c r="E401" s="74"/>
+      <x:c r="F401" s="75"/>
+      <x:c r="G401" s="75"/>
+      <x:c r="H401" s="76"/>
+    </x:row>
+    <x:row r="402">
+      <x:c r="E402" s="74"/>
+      <x:c r="F402" s="75"/>
+      <x:c r="G402" s="75"/>
+      <x:c r="H402" s="76"/>
+    </x:row>
+    <x:row r="403">
+      <x:c r="E403" s="74"/>
+      <x:c r="F403" s="75"/>
+      <x:c r="G403" s="75"/>
+      <x:c r="H403" s="76"/>
+    </x:row>
+    <x:row r="404">
+      <x:c r="E404" s="74"/>
+      <x:c r="F404" s="75"/>
+      <x:c r="G404" s="75"/>
+      <x:c r="H404" s="76"/>
+    </x:row>
+    <x:row r="405">
+      <x:c r="E405" s="74"/>
+      <x:c r="F405" s="75"/>
+      <x:c r="G405" s="75"/>
+      <x:c r="H405" s="76"/>
+    </x:row>
+    <x:row r="406">
+      <x:c r="E406" s="74"/>
+      <x:c r="F406" s="75"/>
+      <x:c r="G406" s="75"/>
+      <x:c r="H406" s="76"/>
+    </x:row>
+    <x:row r="407">
+      <x:c r="E407" s="74"/>
+      <x:c r="F407" s="75"/>
+      <x:c r="G407" s="75"/>
+      <x:c r="H407" s="76"/>
+    </x:row>
+    <x:row r="408">
+      <x:c r="E408" s="74"/>
+      <x:c r="F408" s="75"/>
+      <x:c r="G408" s="75"/>
+      <x:c r="H408" s="76"/>
+    </x:row>
+    <x:row r="409">
+      <x:c r="E409" s="74"/>
+      <x:c r="F409" s="75"/>
+      <x:c r="G409" s="75"/>
+      <x:c r="H409" s="76"/>
+    </x:row>
+    <x:row r="410">
+      <x:c r="E410" s="74"/>
+      <x:c r="F410" s="75"/>
+      <x:c r="G410" s="75"/>
+      <x:c r="H410" s="76"/>
+    </x:row>
+    <x:row r="411">
+      <x:c r="E411" s="74"/>
+      <x:c r="F411" s="75"/>
+      <x:c r="G411" s="75"/>
+      <x:c r="H411" s="76"/>
+    </x:row>
+    <x:row r="412">
+      <x:c r="E412" s="74"/>
+      <x:c r="F412" s="75"/>
+      <x:c r="G412" s="75"/>
+      <x:c r="H412" s="76"/>
+    </x:row>
+    <x:row r="413">
+      <x:c r="E413" s="74"/>
+      <x:c r="F413" s="75"/>
+      <x:c r="G413" s="75"/>
+      <x:c r="H413" s="76"/>
+    </x:row>
+    <x:row r="414">
+      <x:c r="E414" s="74"/>
+      <x:c r="F414" s="75"/>
+      <x:c r="G414" s="75"/>
+      <x:c r="H414" s="76"/>
+    </x:row>
+    <x:row r="415">
+      <x:c r="E415" s="74"/>
+      <x:c r="F415" s="75"/>
+      <x:c r="G415" s="75"/>
+      <x:c r="H415" s="76"/>
+    </x:row>
+    <x:row r="416">
+      <x:c r="E416" s="74"/>
+      <x:c r="F416" s="75"/>
+      <x:c r="G416" s="75"/>
+      <x:c r="H416" s="76"/>
+    </x:row>
+    <x:row r="417">
+      <x:c r="E417" s="74"/>
+      <x:c r="F417" s="75"/>
+      <x:c r="G417" s="75"/>
+      <x:c r="H417" s="76"/>
+    </x:row>
+    <x:row r="418">
+      <x:c r="E418" s="74"/>
+      <x:c r="F418" s="75"/>
+      <x:c r="G418" s="75"/>
+      <x:c r="H418" s="76"/>
+    </x:row>
+    <x:row r="419">
+      <x:c r="E419" s="74"/>
+      <x:c r="F419" s="75"/>
+      <x:c r="G419" s="75"/>
+      <x:c r="H419" s="76"/>
+    </x:row>
+    <x:row r="420">
+      <x:c r="E420" s="74"/>
+      <x:c r="F420" s="75"/>
+      <x:c r="G420" s="75"/>
+      <x:c r="H420" s="76"/>
+    </x:row>
+    <x:row r="421">
+      <x:c r="E421" s="74"/>
+      <x:c r="F421" s="75"/>
+      <x:c r="G421" s="75"/>
+      <x:c r="H421" s="76"/>
+    </x:row>
+    <x:row r="422">
+      <x:c r="E422" s="74"/>
+      <x:c r="F422" s="75"/>
+      <x:c r="G422" s="75"/>
+      <x:c r="H422" s="76"/>
+    </x:row>
+    <x:row r="423">
+      <x:c r="E423" s="74"/>
+      <x:c r="F423" s="75"/>
+      <x:c r="G423" s="75"/>
+      <x:c r="H423" s="76"/>
+    </x:row>
+    <x:row r="424">
+      <x:c r="E424" s="74"/>
+      <x:c r="F424" s="75"/>
+      <x:c r="G424" s="75"/>
+      <x:c r="H424" s="76"/>
+    </x:row>
+    <x:row r="425">
+      <x:c r="E425" s="74"/>
+      <x:c r="F425" s="75"/>
+      <x:c r="G425" s="75"/>
+      <x:c r="H425" s="76"/>
+    </x:row>
+    <x:row r="426">
+      <x:c r="E426" s="74"/>
+      <x:c r="F426" s="75"/>
+      <x:c r="G426" s="75"/>
+      <x:c r="H426" s="76"/>
+    </x:row>
+    <x:row r="427">
+      <x:c r="E427" s="74"/>
+      <x:c r="F427" s="75"/>
+      <x:c r="G427" s="75"/>
+      <x:c r="H427" s="76"/>
+    </x:row>
+    <x:row r="428">
+      <x:c r="E428" s="74"/>
+      <x:c r="F428" s="75"/>
+      <x:c r="G428" s="75"/>
+      <x:c r="H428" s="76"/>
+    </x:row>
+    <x:row r="429">
+      <x:c r="E429" s="74"/>
+      <x:c r="F429" s="75"/>
+      <x:c r="G429" s="75"/>
+      <x:c r="H429" s="76"/>
+    </x:row>
+    <x:row r="430">
+      <x:c r="E430" s="74"/>
+      <x:c r="F430" s="75"/>
+      <x:c r="G430" s="75"/>
+      <x:c r="H430" s="76"/>
+    </x:row>
+    <x:row r="431">
+      <x:c r="E431" s="74"/>
+      <x:c r="F431" s="75"/>
+      <x:c r="G431" s="75"/>
+      <x:c r="H431" s="76"/>
+    </x:row>
+    <x:row r="432">
+      <x:c r="E432" s="74"/>
+      <x:c r="F432" s="75"/>
+      <x:c r="G432" s="75"/>
+      <x:c r="H432" s="76"/>
+    </x:row>
+    <x:row r="433">
+      <x:c r="E433" s="74"/>
+      <x:c r="F433" s="75"/>
+      <x:c r="G433" s="75"/>
+      <x:c r="H433" s="76"/>
+    </x:row>
+    <x:row r="434">
+      <x:c r="E434" s="74"/>
+      <x:c r="F434" s="75"/>
+      <x:c r="G434" s="75"/>
+      <x:c r="H434" s="76"/>
+    </x:row>
+    <x:row r="435">
+      <x:c r="E435" s="74"/>
+      <x:c r="F435" s="75"/>
+      <x:c r="G435" s="75"/>
+      <x:c r="H435" s="76"/>
+    </x:row>
+    <x:row r="436">
+      <x:c r="E436" s="74"/>
+      <x:c r="F436" s="75"/>
+      <x:c r="G436" s="75"/>
+      <x:c r="H436" s="76"/>
+    </x:row>
+    <x:row r="437">
+      <x:c r="E437" s="74"/>
+      <x:c r="F437" s="75"/>
+      <x:c r="G437" s="75"/>
+      <x:c r="H437" s="76"/>
+    </x:row>
+    <x:row r="438">
+      <x:c r="E438" s="74"/>
+      <x:c r="F438" s="75"/>
+      <x:c r="G438" s="75"/>
+      <x:c r="H438" s="76"/>
+    </x:row>
+    <x:row r="439">
+      <x:c r="E439" s="74"/>
+      <x:c r="F439" s="75"/>
+      <x:c r="G439" s="75"/>
+      <x:c r="H439" s="76"/>
+    </x:row>
+    <x:row r="440">
+      <x:c r="E440" s="74"/>
+      <x:c r="F440" s="75"/>
+      <x:c r="G440" s="75"/>
+      <x:c r="H440" s="76"/>
+    </x:row>
+    <x:row r="441">
+      <x:c r="E441" s="74"/>
+      <x:c r="F441" s="75"/>
+      <x:c r="G441" s="75"/>
+      <x:c r="H441" s="76"/>
+    </x:row>
+    <x:row r="442">
+      <x:c r="E442" s="74"/>
+      <x:c r="F442" s="75"/>
+      <x:c r="G442" s="75"/>
+      <x:c r="H442" s="76"/>
+    </x:row>
+    <x:row r="443">
+      <x:c r="E443" s="74"/>
+      <x:c r="F443" s="75"/>
+      <x:c r="G443" s="75"/>
+      <x:c r="H443" s="76"/>
+    </x:row>
+    <x:row r="444">
+      <x:c r="E444" s="74"/>
+      <x:c r="F444" s="75"/>
+      <x:c r="G444" s="75"/>
+      <x:c r="H444" s="76"/>
+    </x:row>
+    <x:row r="445">
+      <x:c r="E445" s="74"/>
+      <x:c r="F445" s="75"/>
+      <x:c r="G445" s="75"/>
+      <x:c r="H445" s="76"/>
+    </x:row>
+    <x:row r="446">
+      <x:c r="E446" s="74"/>
+      <x:c r="F446" s="75"/>
+      <x:c r="G446" s="75"/>
+      <x:c r="H446" s="76"/>
+    </x:row>
+    <x:row r="447">
+      <x:c r="E447" s="74"/>
+      <x:c r="F447" s="75"/>
+      <x:c r="G447" s="75"/>
+      <x:c r="H447" s="76"/>
+    </x:row>
+    <x:row r="448">
+      <x:c r="E448" s="74"/>
+      <x:c r="F448" s="75"/>
+      <x:c r="G448" s="75"/>
+      <x:c r="H448" s="76"/>
+    </x:row>
+    <x:row r="449">
+      <x:c r="E449" s="74"/>
+      <x:c r="F449" s="75"/>
+      <x:c r="G449" s="75"/>
+      <x:c r="H449" s="76"/>
+    </x:row>
+    <x:row r="450">
+      <x:c r="E450" s="74"/>
+      <x:c r="F450" s="75"/>
+      <x:c r="G450" s="75"/>
+      <x:c r="H450" s="76"/>
+    </x:row>
+    <x:row r="451">
+      <x:c r="E451" s="74"/>
+      <x:c r="F451" s="75"/>
+      <x:c r="G451" s="75"/>
+      <x:c r="H451" s="76"/>
+    </x:row>
+    <x:row r="452">
+      <x:c r="E452" s="74"/>
+      <x:c r="F452" s="75"/>
+      <x:c r="G452" s="75"/>
+      <x:c r="H452" s="76"/>
+    </x:row>
+    <x:row r="453">
+      <x:c r="E453" s="74"/>
+      <x:c r="F453" s="75"/>
+      <x:c r="G453" s="75"/>
+      <x:c r="H453" s="76"/>
+    </x:row>
+    <x:row r="454">
+      <x:c r="E454" s="74"/>
+      <x:c r="F454" s="75"/>
+      <x:c r="G454" s="75"/>
+      <x:c r="H454" s="76"/>
+    </x:row>
+    <x:row r="455">
+      <x:c r="E455" s="74"/>
+      <x:c r="F455" s="75"/>
+      <x:c r="G455" s="75"/>
+      <x:c r="H455" s="76"/>
+    </x:row>
+    <x:row r="456">
+      <x:c r="E456" s="74"/>
+      <x:c r="F456" s="75"/>
+      <x:c r="G456" s="75"/>
+      <x:c r="H456" s="76"/>
+    </x:row>
+    <x:row r="457">
+      <x:c r="E457" s="74"/>
+      <x:c r="F457" s="75"/>
+      <x:c r="G457" s="75"/>
+      <x:c r="H457" s="76"/>
+    </x:row>
+    <x:row r="458">
+      <x:c r="E458" s="74"/>
+      <x:c r="F458" s="75"/>
+      <x:c r="G458" s="75"/>
+      <x:c r="H458" s="76"/>
+    </x:row>
+    <x:row r="459">
+      <x:c r="E459" s="74"/>
+      <x:c r="F459" s="75"/>
+      <x:c r="G459" s="75"/>
+      <x:c r="H459" s="76"/>
+    </x:row>
+    <x:row r="460">
+      <x:c r="E460" s="74"/>
+      <x:c r="F460" s="75"/>
+      <x:c r="G460" s="75"/>
+      <x:c r="H460" s="76"/>
+    </x:row>
+    <x:row r="461">
+      <x:c r="E461" s="74"/>
+      <x:c r="F461" s="75"/>
+      <x:c r="G461" s="75"/>
+      <x:c r="H461" s="76"/>
+    </x:row>
+    <x:row r="462">
+      <x:c r="E462" s="74"/>
+      <x:c r="F462" s="75"/>
+      <x:c r="G462" s="75"/>
+      <x:c r="H462" s="76"/>
+    </x:row>
+    <x:row r="463">
+      <x:c r="E463" s="74"/>
+      <x:c r="F463" s="75"/>
+      <x:c r="G463" s="75"/>
+      <x:c r="H463" s="76"/>
+    </x:row>
+    <x:row r="464">
+      <x:c r="E464" s="74"/>
+      <x:c r="F464" s="75"/>
+      <x:c r="G464" s="75"/>
+      <x:c r="H464" s="76"/>
+    </x:row>
+    <x:row r="465">
+      <x:c r="E465" s="74"/>
+      <x:c r="F465" s="75"/>
+      <x:c r="G465" s="75"/>
+      <x:c r="H465" s="76"/>
+    </x:row>
+    <x:row r="466">
+      <x:c r="E466" s="74"/>
+      <x:c r="F466" s="75"/>
+      <x:c r="G466" s="75"/>
+      <x:c r="H466" s="76"/>
+    </x:row>
+    <x:row r="467">
+      <x:c r="E467" s="74"/>
+      <x:c r="F467" s="75"/>
+      <x:c r="G467" s="75"/>
+      <x:c r="H467" s="76"/>
+    </x:row>
+    <x:row r="468">
+      <x:c r="E468" s="74"/>
+      <x:c r="F468" s="75"/>
+      <x:c r="G468" s="75"/>
+      <x:c r="H468" s="76"/>
+    </x:row>
+    <x:row r="469">
+      <x:c r="E469" s="74"/>
+      <x:c r="F469" s="75"/>
+      <x:c r="G469" s="75"/>
+      <x:c r="H469" s="76"/>
+    </x:row>
+    <x:row r="470">
+      <x:c r="E470" s="74"/>
+      <x:c r="F470" s="75"/>
+      <x:c r="G470" s="75"/>
+      <x:c r="H470" s="76"/>
+    </x:row>
+    <x:row r="471">
+      <x:c r="E471" s="74"/>
+      <x:c r="F471" s="75"/>
+      <x:c r="G471" s="75"/>
+      <x:c r="H471" s="76"/>
+    </x:row>
+    <x:row r="472">
+      <x:c r="E472" s="74"/>
+      <x:c r="F472" s="75"/>
+      <x:c r="G472" s="75"/>
+      <x:c r="H472" s="76"/>
+    </x:row>
+    <x:row r="473">
+      <x:c r="E473" s="74"/>
+      <x:c r="F473" s="75"/>
+      <x:c r="G473" s="75"/>
+      <x:c r="H473" s="76"/>
+    </x:row>
+    <x:row r="474">
+      <x:c r="E474" s="74"/>
+      <x:c r="F474" s="75"/>
+      <x:c r="G474" s="75"/>
+      <x:c r="H474" s="76"/>
+    </x:row>
+    <x:row r="475">
+      <x:c r="E475" s="74"/>
+      <x:c r="F475" s="75"/>
+      <x:c r="G475" s="75"/>
+      <x:c r="H475" s="76"/>
+    </x:row>
+    <x:row r="476">
+      <x:c r="E476" s="74"/>
+      <x:c r="F476" s="75"/>
+      <x:c r="G476" s="75"/>
+      <x:c r="H476" s="76"/>
+    </x:row>
+    <x:row r="477">
+      <x:c r="E477" s="74"/>
+      <x:c r="F477" s="75"/>
+      <x:c r="G477" s="75"/>
+      <x:c r="H477" s="76"/>
+    </x:row>
+    <x:row r="478">
+      <x:c r="E478" s="74"/>
+      <x:c r="F478" s="75"/>
+      <x:c r="G478" s="75"/>
+      <x:c r="H478" s="76"/>
+    </x:row>
+    <x:row r="479">
+      <x:c r="E479" s="74"/>
+      <x:c r="F479" s="75"/>
+      <x:c r="G479" s="75"/>
+      <x:c r="H479" s="76"/>
+    </x:row>
+    <x:row r="480">
+      <x:c r="E480" s="74"/>
+      <x:c r="F480" s="75"/>
+      <x:c r="G480" s="75"/>
+      <x:c r="H480" s="76"/>
+    </x:row>
+    <x:row r="481">
+      <x:c r="E481" s="74"/>
+      <x:c r="F481" s="75"/>
+      <x:c r="G481" s="75"/>
+      <x:c r="H481" s="76"/>
+    </x:row>
+    <x:row r="482">
+      <x:c r="E482" s="74"/>
+      <x:c r="F482" s="75"/>
+      <x:c r="G482" s="75"/>
+      <x:c r="H482" s="76"/>
+    </x:row>
+    <x:row r="483">
+      <x:c r="E483" s="74"/>
+      <x:c r="F483" s="75"/>
+      <x:c r="G483" s="75"/>
+      <x:c r="H483" s="76"/>
+    </x:row>
+    <x:row r="484">
+      <x:c r="E484" s="74"/>
+      <x:c r="F484" s="75"/>
+      <x:c r="G484" s="75"/>
+      <x:c r="H484" s="76"/>
+    </x:row>
+    <x:row r="485">
+      <x:c r="E485" s="74"/>
+      <x:c r="F485" s="75"/>
+      <x:c r="G485" s="75"/>
+      <x:c r="H485" s="76"/>
+    </x:row>
+    <x:row r="486">
+      <x:c r="E486" s="74"/>
+      <x:c r="F486" s="75"/>
+      <x:c r="G486" s="75"/>
+      <x:c r="H486" s="76"/>
+    </x:row>
+    <x:row r="487">
+      <x:c r="E487" s="74"/>
+      <x:c r="F487" s="75"/>
+      <x:c r="G487" s="75"/>
+      <x:c r="H487" s="76"/>
+    </x:row>
+    <x:row r="488">
+      <x:c r="E488" s="74"/>
+      <x:c r="F488" s="75"/>
+      <x:c r="G488" s="75"/>
+      <x:c r="H488" s="76"/>
+    </x:row>
+    <x:row r="489">
+      <x:c r="E489" s="74"/>
+      <x:c r="F489" s="75"/>
+      <x:c r="G489" s="75"/>
+      <x:c r="H489" s="76"/>
+    </x:row>
+    <x:row r="490">
+      <x:c r="E490" s="74"/>
+      <x:c r="F490" s="75"/>
+      <x:c r="G490" s="75"/>
+      <x:c r="H490" s="76"/>
+    </x:row>
+    <x:row r="491">
+      <x:c r="E491" s="74"/>
+      <x:c r="F491" s="75"/>
+      <x:c r="G491" s="75"/>
+      <x:c r="H491" s="76"/>
+    </x:row>
+    <x:row r="492">
+      <x:c r="E492" s="74"/>
+      <x:c r="F492" s="75"/>
+      <x:c r="G492" s="75"/>
+      <x:c r="H492" s="76"/>
+    </x:row>
+    <x:row r="493">
+      <x:c r="E493" s="74"/>
+      <x:c r="F493" s="75"/>
+      <x:c r="G493" s="75"/>
+      <x:c r="H493" s="76"/>
+    </x:row>
+    <x:row r="494">
+      <x:c r="E494" s="74"/>
+      <x:c r="F494" s="75"/>
+      <x:c r="G494" s="75"/>
+      <x:c r="H494" s="76"/>
+    </x:row>
+    <x:row r="495">
+      <x:c r="E495" s="74"/>
+      <x:c r="F495" s="75"/>
+      <x:c r="G495" s="75"/>
+      <x:c r="H495" s="76"/>
+    </x:row>
+    <x:row r="496">
+      <x:c r="E496" s="74"/>
+      <x:c r="F496" s="75"/>
+      <x:c r="G496" s="75"/>
+      <x:c r="H496" s="76"/>
+    </x:row>
+    <x:row r="497">
+      <x:c r="E497" s="74"/>
+      <x:c r="F497" s="75"/>
+      <x:c r="G497" s="75"/>
+      <x:c r="H497" s="76"/>
+    </x:row>
+    <x:row r="498">
+      <x:c r="E498" s="74"/>
+      <x:c r="F498" s="75"/>
+      <x:c r="G498" s="75"/>
+      <x:c r="H498" s="76"/>
+    </x:row>
+    <x:row r="499">
+      <x:c r="E499" s="74"/>
+      <x:c r="F499" s="75"/>
+      <x:c r="G499" s="75"/>
+      <x:c r="H499" s="76"/>
+    </x:row>
+    <x:row r="500">
+      <x:c r="E500" s="74"/>
+      <x:c r="F500" s="75"/>
+      <x:c r="G500" s="75"/>
+      <x:c r="H500" s="76"/>
+    </x:row>
   </x:sheetData>
-  <x:dataValidations count="7">
+  <x:dataValidations count="13">
     <x:dataValidation type="list" sqref="C2:C201">
       <x:formula1>"Projeto,Processo,Programa,Contrato,Aquisição"</x:formula1>
     </x:dataValidation>
@@ -4287,6 +6210,24 @@
     <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="E2:E201">
       <x:formula1>0</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="C2:C500">
+      <x:formula1>"Projeto,Processo,Programa,Contrato,Aquisição"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="D2:D500">
+      <x:formula1>"Baixa,Média,Alta"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="I2:I500">
+      <x:formula1>"À iniciar,Em execução"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="J2:J500">
+      <x:formula1>"Construção,Reforma,Licitação,Modernização"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="L2:L500">
+      <x:formula1>'VALORES ACEITOS'!$A$2:$A$8</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="M2:M500">
+      <x:formula1>'VALORES ACEITOS'!$B$2:$B$17</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4306,7 +6247,7 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="55" t="str">
-        <x:v>MODELO DE IMPORTAÇÃO — MONITORAMENTO E CONTROLE SEMED</x:v>
+        <x:v>MODELO DE IMPORTAÇÃO — MONITORAMENTO E CONTROLE SEMED · ATUALIZADO EM 26/08/2026</x:v>
       </x:c>
       <x:c r="B1" s="55"/>
       <x:c r="C1" s="55"/>
@@ -4577,7 +6518,7 @@
         <x:v>LISTA</x:v>
       </x:c>
       <x:c r="D23" s="69" t="str">
-        <x:v>Selecione um dos valores da aba VALORES ACEITOS.</x:v>
+        <x:v>Selecione uma Área Principal cadastrada na aba VALORES ACEITOS.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -4588,10 +6529,10 @@
         <x:v>SIM</x:v>
       </x:c>
       <x:c r="C24" s="68" t="str">
-        <x:v>LISTA CONDICIONAL</x:v>
+        <x:v>LISTA</x:v>
       </x:c>
       <x:c r="D24" s="69" t="str">
-        <x:v>Deve ser compatível com a Área Principal conforme a aba VALORES ACEITOS.</x:v>
+        <x:v>Selecione uma Área Secundária cadastrada na aba VALORES ACEITOS.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -4607,6 +6548,12 @@
       <x:c r="D25" s="69" t="str">
         <x:v>Texto livre em caixa alta.</x:v>
       </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="79"/>
+      <x:c r="B27" s="79"/>
+      <x:c r="C27" s="79"/>
+      <x:c r="D27" s="79"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4617,6 +6564,7 @@
     <x:mergeCell ref="B7:F7"/>
     <x:mergeCell ref="B8:F8"/>
     <x:mergeCell ref="B9:F9"/>
+    <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4626,72 +6574,126 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="48" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="92" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="73" t="str">
+      <x:c r="A1" s="94" t="str">
         <x:v>ÁREA PRINCIPAL</x:v>
       </x:c>
-      <x:c r="B1" s="73" t="str">
-        <x:v>ÁREAS SECUNDÁRIAS ACEITAS</x:v>
+      <x:c r="B1" s="94" t="str">
+        <x:v>ÁREA SECUNDÁRIA</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
-      <x:c r="A2" s="69" t="str">
+      <x:c r="A2" s="95" t="str">
         <x:v>Gabinete do Secretário(a)</x:v>
       </x:c>
-      <x:c r="B2" s="69" t="str">
-        <x:v>TODAS AS OPÇÕES</x:v>
+      <x:c r="B2" s="95" t="str">
+        <x:v>Educação Infantil</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="34" customHeight="1">
-      <x:c r="A3" s="69" t="str">
+      <x:c r="A3" s="95" t="str">
         <x:v>Assessoria de Comunicação</x:v>
       </x:c>
-      <x:c r="B3" s="69" t="str">
-        <x:v>TODAS AS OPÇÕES</x:v>
+      <x:c r="B3" s="95" t="str">
+        <x:v>Educação Fundamental</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
-      <x:c r="A4" s="69" t="str">
+      <x:c r="A4" s="95" t="str">
         <x:v>Assessoria Jurídica</x:v>
       </x:c>
-      <x:c r="B4" s="69" t="str">
-        <x:v>TODAS AS OPÇÕES</x:v>
+      <x:c r="B4" s="95" t="str">
+        <x:v>DETIC</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="69" t="str">
+      <x:c r="A5" s="95" t="str">
         <x:v>Diretoria de Ensino</x:v>
       </x:c>
-      <x:c r="B5" s="69" t="str">
-        <x:v>Educação Infantil; Educação Fundamental; DETIC; Inspeção; Núcleo de Avaliação</x:v>
+      <x:c r="B5" s="95" t="str">
+        <x:v>Inspeção</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="69" t="str">
+      <x:c r="A6" s="95" t="str">
         <x:v>Diretoria de Apoio à Educação Básica</x:v>
       </x:c>
-      <x:c r="B6" s="69" t="str">
-        <x:v>Arte e Cultura; CREI; CEMEA Boa Vista; CEU das Artes; Biblioteca</x:v>
+      <x:c r="B6" s="95" t="str">
+        <x:v>Núcleo de Avaliação</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
-      <x:c r="A7" s="69" t="str">
+      <x:c r="A7" s="95" t="str">
         <x:v>Diretoria de Logística</x:v>
       </x:c>
-      <x:c r="B7" s="69" t="str">
-        <x:v>Infraestrutura; Recursos Humanos; Patrimônio; Transporte; Nutrição</x:v>
+      <x:c r="B7" s="95" t="str">
+        <x:v>Transporte</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="34" customHeight="1">
-      <x:c r="A8" s="69" t="str">
+      <x:c r="A8" s="95" t="str">
         <x:v>Diretoria de Planejamento Gestão e Finanças</x:v>
       </x:c>
-      <x:c r="B8" s="69" t="str">
-        <x:v>Programas Federais; Monitoramento de Contratos; Planejamento</x:v>
+      <x:c r="B8" s="95" t="str">
+        <x:v>Patrimônio</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="96" t="str"/>
+      <x:c r="B9" s="97" t="str">
+        <x:v>Infraestrutura</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="96" t="str"/>
+      <x:c r="B10" s="97" t="str">
+        <x:v>Recursos Humanos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="96" t="str"/>
+      <x:c r="B11" s="97" t="str">
+        <x:v>Monitoramento de Contratos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="96" t="str"/>
+      <x:c r="B12" s="97" t="str">
+        <x:v>Programas Federais</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="96" t="str"/>
+      <x:c r="B13" s="97" t="str">
+        <x:v>Planejamento</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="96" t="str"/>
+      <x:c r="B14" s="97" t="str">
+        <x:v>Arte e Cultura</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="96" t="str"/>
+      <x:c r="B15" s="97" t="str">
+        <x:v>Céu das Artes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="96" t="str"/>
+      <x:c r="B16" s="97" t="str">
+        <x:v>CREI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="98" t="str"/>
+      <x:c r="B17" s="99" t="str">
+        <x:v>CEMEA Boa Vista</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
